--- a/data/ams_weekly_data/White_Mulberry/ads_report_week31.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week31.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -714,7 +703,7 @@
         <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>28922</v>
+        <v>28921</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1022,7 +1011,7 @@
         <v>248</v>
       </c>
       <c r="F21" t="n">
-        <v>24976</v>
+        <v>24975</v>
       </c>
       <c r="G21" t="n">
         <v>14574.58</v>
@@ -1137,10 +1126,10 @@
         <v>29162</v>
       </c>
       <c r="G25" t="n">
-        <v>5082.2</v>
+        <v>6776.27</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1417,10 +1406,10 @@
         <v>27454</v>
       </c>
       <c r="G35" t="n">
-        <v>17494.06</v>
+        <v>22154.23</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1946,13 +1935,13 @@
         <v>138</v>
       </c>
       <c r="F54" t="n">
-        <v>16993</v>
+        <v>16992</v>
       </c>
       <c r="G54" t="n">
-        <v>8131.36</v>
+        <v>8681.360000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -2114,7 +2103,7 @@
         <v>45</v>
       </c>
       <c r="F60" t="n">
-        <v>5062</v>
+        <v>5061</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2145,10 +2134,10 @@
         <v>6277</v>
       </c>
       <c r="G61" t="n">
-        <v>11014.41</v>
+        <v>7371.19</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2254,7 +2243,7 @@
         <v>324</v>
       </c>
       <c r="F65" t="n">
-        <v>20505</v>
+        <v>20503</v>
       </c>
       <c r="G65" t="n">
         <v>7287.29</v>
@@ -2282,7 +2271,7 @@
         <v>76</v>
       </c>
       <c r="F66" t="n">
-        <v>6959</v>
+        <v>6957</v>
       </c>
       <c r="G66" t="n">
         <v>7117.8</v>
@@ -2394,7 +2383,7 @@
         <v>140</v>
       </c>
       <c r="F70" t="n">
-        <v>13515</v>
+        <v>13513</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2618,7 +2607,7 @@
         <v>145</v>
       </c>
       <c r="F78" t="n">
-        <v>15283</v>
+        <v>15282</v>
       </c>
       <c r="G78" t="n">
         <v>7033.05</v>
@@ -2674,7 +2663,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2702,7 +2691,7 @@
         <v>73</v>
       </c>
       <c r="F81" t="n">
-        <v>12820</v>
+        <v>12819</v>
       </c>
       <c r="G81" t="n">
         <v>7033.05</v>
@@ -2954,7 +2943,7 @@
         <v>117</v>
       </c>
       <c r="F90" t="n">
-        <v>18154</v>
+        <v>18148</v>
       </c>
       <c r="G90" t="n">
         <v>11944.91</v>
@@ -3153,10 +3142,10 @@
         <v>7602</v>
       </c>
       <c r="G97" t="n">
-        <v>21263.55</v>
+        <v>26007.62</v>
       </c>
       <c r="H97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -3262,7 +3251,7 @@
         <v>121</v>
       </c>
       <c r="F101" t="n">
-        <v>57356</v>
+        <v>57355</v>
       </c>
       <c r="G101" t="n">
         <v>3388.13</v>
@@ -3293,10 +3282,10 @@
         <v>39559</v>
       </c>
       <c r="G102" t="n">
-        <v>23886.44</v>
+        <v>25580.51</v>
       </c>
       <c r="H102" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103">
@@ -3430,7 +3419,7 @@
         <v>29</v>
       </c>
       <c r="F107" t="n">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="G107" t="n">
         <v>4214.42</v>
@@ -3461,10 +3450,10 @@
         <v>16616</v>
       </c>
       <c r="G108" t="n">
-        <v>4103.39</v>
+        <v>3595.77</v>
       </c>
       <c r="H108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -3542,7 +3531,7 @@
         <v>95</v>
       </c>
       <c r="F111" t="n">
-        <v>29210</v>
+        <v>29208</v>
       </c>
       <c r="G111" t="n">
         <v>3049.16</v>
@@ -3650,42 +3639,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4501,6 +4490,529 @@
       </c>
       <c r="H30" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3430</v>
+      </c>
+      <c r="E2" t="n">
+        <v>124</v>
+      </c>
+      <c r="F2" t="n">
+        <v>353.15</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10591.105</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3430</v>
+      </c>
+      <c r="E3" t="n">
+        <v>124</v>
+      </c>
+      <c r="F3" t="n">
+        <v>353.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10591.105</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>300.0075</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3516.5275</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" t="n">
+        <v>300.0075</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3516.5275</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>300.0075</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3516.5275</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7544</v>
+      </c>
+      <c r="E7" t="n">
+        <v>41</v>
+      </c>
+      <c r="F7" t="n">
+        <v>300.0075</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3516.5275</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- B0DB5VG39T- Exact</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21601</v>
+      </c>
+      <c r="E8" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" t="n">
+        <v>678.5700000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10119</v>
+      </c>
+      <c r="E9" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>624.7072308032597</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3471.868791047113</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19017</v>
+      </c>
+      <c r="E10" t="n">
+        <v>67</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1174.02276919674</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6524.741208952887</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>155</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>66.17999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>23721</v>
+      </c>
+      <c r="E12" t="n">
+        <v>231</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3064.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13977.96</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10377</v>
+      </c>
+      <c r="E13" t="n">
+        <v>131</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1582.461396091352</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4659.851297892206</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6225</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78</v>
+      </c>
+      <c r="F14" t="n">
+        <v>949.248603908648</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2795.238702107794</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-KT-SBV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>25221</v>
+      </c>
+      <c r="E15" t="n">
+        <v>187</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2733.23</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4193.22</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week31.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week31.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -703,7 +715,7 @@
         <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>28921</v>
+        <v>28922</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1011,7 +1023,7 @@
         <v>248</v>
       </c>
       <c r="F21" t="n">
-        <v>24975</v>
+        <v>24976</v>
       </c>
       <c r="G21" t="n">
         <v>14574.58</v>
@@ -1126,10 +1138,10 @@
         <v>29162</v>
       </c>
       <c r="G25" t="n">
-        <v>6776.27</v>
+        <v>5082.2</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1406,10 +1418,10 @@
         <v>27454</v>
       </c>
       <c r="G35" t="n">
-        <v>22154.23</v>
+        <v>17494.06</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1935,13 +1947,13 @@
         <v>138</v>
       </c>
       <c r="F54" t="n">
-        <v>16992</v>
+        <v>16993</v>
       </c>
       <c r="G54" t="n">
-        <v>8681.360000000001</v>
+        <v>8131.36</v>
       </c>
       <c r="H54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -2103,7 +2115,7 @@
         <v>45</v>
       </c>
       <c r="F60" t="n">
-        <v>5061</v>
+        <v>5062</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2134,10 +2146,10 @@
         <v>6277</v>
       </c>
       <c r="G61" t="n">
-        <v>7371.19</v>
+        <v>11014.41</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -2243,7 +2255,7 @@
         <v>324</v>
       </c>
       <c r="F65" t="n">
-        <v>20503</v>
+        <v>20505</v>
       </c>
       <c r="G65" t="n">
         <v>7287.29</v>
@@ -2271,7 +2283,7 @@
         <v>76</v>
       </c>
       <c r="F66" t="n">
-        <v>6957</v>
+        <v>6959</v>
       </c>
       <c r="G66" t="n">
         <v>7117.8</v>
@@ -2383,7 +2395,7 @@
         <v>140</v>
       </c>
       <c r="F70" t="n">
-        <v>13513</v>
+        <v>13515</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2607,7 +2619,7 @@
         <v>145</v>
       </c>
       <c r="F78" t="n">
-        <v>15282</v>
+        <v>15283</v>
       </c>
       <c r="G78" t="n">
         <v>7033.05</v>
@@ -2663,7 +2675,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2691,7 +2703,7 @@
         <v>73</v>
       </c>
       <c r="F81" t="n">
-        <v>12819</v>
+        <v>12820</v>
       </c>
       <c r="G81" t="n">
         <v>7033.05</v>
@@ -2943,7 +2955,7 @@
         <v>117</v>
       </c>
       <c r="F90" t="n">
-        <v>18148</v>
+        <v>18154</v>
       </c>
       <c r="G90" t="n">
         <v>11944.91</v>
@@ -3142,10 +3154,10 @@
         <v>7602</v>
       </c>
       <c r="G97" t="n">
-        <v>26007.62</v>
+        <v>21263.55</v>
       </c>
       <c r="H97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -3251,7 +3263,7 @@
         <v>121</v>
       </c>
       <c r="F101" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="G101" t="n">
         <v>3388.13</v>
@@ -3282,10 +3294,10 @@
         <v>39559</v>
       </c>
       <c r="G102" t="n">
-        <v>25580.51</v>
+        <v>23886.44</v>
       </c>
       <c r="H102" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
@@ -3419,7 +3431,7 @@
         <v>29</v>
       </c>
       <c r="F107" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G107" t="n">
         <v>4214.42</v>
@@ -3450,10 +3462,10 @@
         <v>16616</v>
       </c>
       <c r="G108" t="n">
-        <v>3595.77</v>
+        <v>4103.39</v>
       </c>
       <c r="H108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3531,7 +3543,7 @@
         <v>95</v>
       </c>
       <c r="F111" t="n">
-        <v>29208</v>
+        <v>29210</v>
       </c>
       <c r="G111" t="n">
         <v>3049.16</v>
@@ -3639,42 +3651,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4507,47 +4519,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
